--- a/database/event/4490/event_4490_evp_summary.xlsx
+++ b/database/event/4490/event_4490_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.3028</v>
+        <v>10.2605</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1446</v>
+        <v>4.1276</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7407</v>
+        <v>3.6439</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3028</v>
+        <v>10.2605</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7926</v>
+        <v>3.7503</v>
       </c>
       <c r="G2" t="n">
         <v>6.5103</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7926</v>
+        <v>3.7503</v>
       </c>
       <c r="I2" t="n">
         <v>3.8458</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7437</v>
+        <v>7.7092</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1152</v>
+        <v>3.1013</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7069</v>
+        <v>2.6274</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7437</v>
+        <v>7.7092</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1015</v>
+        <v>3.0669</v>
       </c>
       <c r="G3" t="n">
         <v>4.6422</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1015</v>
+        <v>3.0669</v>
       </c>
       <c r="I3" t="n">
         <v>3.145</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4053</v>
+        <v>6.3723</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5767</v>
+        <v>2.5635</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1662</v>
+        <v>2.0948</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4053</v>
+        <v>6.3723</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9587</v>
+        <v>2.9257</v>
       </c>
       <c r="G4" t="n">
         <v>3.4466</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9587</v>
+        <v>2.9257</v>
       </c>
       <c r="I4" t="n">
         <v>3.0002</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1127</v>
+        <v>5.0743</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0568</v>
+        <v>2.0413</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6441</v>
+        <v>1.5777</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1127</v>
+        <v>5.0743</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4352</v>
+        <v>3.3968</v>
       </c>
       <c r="G5" t="n">
         <v>1.6775</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4352</v>
+        <v>3.3968</v>
       </c>
       <c r="I5" t="n">
         <v>3.4833</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1409</v>
+        <v>4.1659</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6658</v>
+        <v>1.6759</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2515</v>
+        <v>1.2158</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1409</v>
+        <v>4.1659</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6053</v>
+        <v>4.6303</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4644</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9679</v>
+        <v>6.0684</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8371</v>
+        <v>4.9186</v>
       </c>
       <c r="J6" t="n">
         <v>-0.4644</v>
@@ -713,7 +713,7 @@
         <v>60</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3727</v>
+        <v>4.454199999999999</v>
       </c>
       <c r="N6" t="n">
         <v>181</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9221</v>
+        <v>3.9108</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5778</v>
+        <v>1.5732</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1631</v>
+        <v>1.1142</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9221</v>
+        <v>3.9108</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0358</v>
+        <v>3.0245</v>
       </c>
       <c r="G7" t="n">
         <v>0.8863</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0358</v>
+        <v>3.0245</v>
       </c>
       <c r="I7" t="n">
         <v>3.0499</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7275</v>
+        <v>3.7767</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4995</v>
+        <v>1.5193</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0845</v>
+        <v>1.0607</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7275</v>
+        <v>3.7767</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5228</v>
+        <v>3.1659</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2047</v>
+        <v>0.6108</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5228</v>
+        <v>3.1659</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5722</v>
+        <v>3.1925</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2047</v>
+        <v>0.6108</v>
       </c>
       <c r="K8" t="n">
+        <v>152</v>
+      </c>
+      <c r="L8" t="n">
+        <v>79</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.8033</v>
+      </c>
+      <c r="N8" t="n">
         <v>231</v>
-      </c>
-      <c r="L8" t="n">
-        <v>257</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.7769</v>
-      </c>
-      <c r="N8" t="n">
-        <v>488</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7019</v>
+        <v>3.7123</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4892</v>
+        <v>1.4934</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0741</v>
+        <v>1.0351</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7019</v>
+        <v>3.7123</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4294</v>
+        <v>2.8617</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7275</v>
+        <v>0.8506</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2602</v>
+        <v>2.8617</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2635</v>
+        <v>2.3195</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7275</v>
+        <v>0.8506</v>
       </c>
       <c r="K9" t="n">
         <v>121</v>
@@ -851,7 +851,7 @@
         <v>60</v>
       </c>
       <c r="M9" t="n">
-        <v>3.536</v>
+        <v>3.1701</v>
       </c>
       <c r="N9" t="n">
         <v>181</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.616</v>
+        <v>3.7019</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4547</v>
+        <v>1.4892</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0394</v>
+        <v>1.0309</v>
       </c>
       <c r="E10" t="n">
-        <v>3.616</v>
+        <v>3.7019</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5506</v>
+        <v>4.4294</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0654</v>
+        <v>-0.7275</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5506</v>
+        <v>5.2602</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5723</v>
+        <v>4.2635</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0654</v>
+        <v>-0.7275</v>
       </c>
       <c r="K10" t="n">
-        <v>215</v>
+        <v>121</v>
       </c>
       <c r="L10" t="n">
-        <v>267</v>
+        <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6377</v>
+        <v>3.536</v>
       </c>
       <c r="N10" t="n">
-        <v>482</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5002</v>
+        <v>3.6882</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4081</v>
+        <v>1.4837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9926</v>
+        <v>1.0255</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5002</v>
+        <v>3.6882</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6496</v>
+        <v>3.4835</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8506</v>
+        <v>0.2047</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6496</v>
+        <v>3.4835</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1475</v>
+        <v>3.5722</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8506</v>
+        <v>0.2047</v>
       </c>
       <c r="K11" t="n">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>257</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9981</v>
+        <v>3.7769</v>
       </c>
       <c r="N11" t="n">
-        <v>181</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4661</v>
+        <v>3.5987</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3944</v>
+        <v>1.4477</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9789</v>
+        <v>0.9898</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4661</v>
+        <v>3.5987</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8553</v>
+        <v>1.5333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6108</v>
+        <v>2.0654</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8553</v>
+        <v>1.5333</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8686</v>
+        <v>1.5723</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6108</v>
+        <v>2.0654</v>
       </c>
       <c r="K12" t="n">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="L12" t="n">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4794</v>
+        <v>3.6377</v>
       </c>
       <c r="N12" t="n">
-        <v>231</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1289</v>
+        <v>3.3296</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2587</v>
+        <v>1.3394</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8426</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1289</v>
+        <v>3.3296</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9931</v>
+        <v>2.1938</v>
       </c>
       <c r="G13" t="n">
         <v>1.1358</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9931</v>
+        <v>2.1938</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6155</v>
+        <v>1.7781</v>
       </c>
       <c r="J13" t="n">
         <v>1.1358</v>
@@ -1035,7 +1035,7 @@
         <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7513</v>
+        <v>2.9139</v>
       </c>
       <c r="N13" t="n">
         <v>285</v>
@@ -1054,7 +1054,7 @@
         <v>1.1406</v>
       </c>
       <c r="D14" t="n">
-        <v>0.724</v>
+        <v>0.6856</v>
       </c>
       <c r="E14" t="n">
         <v>2.8352</v>
@@ -1090,400 +1090,400 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3779</v>
+        <v>2.4626</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9566</v>
+        <v>0.9907</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5393</v>
+        <v>0.5372</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3779</v>
+        <v>2.4626</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3576</v>
+        <v>2.4626</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0202</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3576</v>
+        <v>2.4626</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3767</v>
+        <v>2.4626</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0202</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>231</v>
+        <v>155</v>
       </c>
       <c r="L15" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3969</v>
+        <v>2.4626</v>
       </c>
       <c r="N15" t="n">
-        <v>488</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1027</v>
+        <v>2.4279</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8459</v>
+        <v>0.9767</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4281</v>
+        <v>0.5234</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1027</v>
+        <v>2.4279</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09619999999999999</v>
+        <v>1.4077</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1989</v>
+        <v>1.0202</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.09619999999999999</v>
+        <v>1.4077</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09760000000000001</v>
+        <v>1.4435</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1989</v>
+        <v>1.0202</v>
       </c>
       <c r="K16" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="L16" t="n">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1013</v>
+        <v>2.4637</v>
       </c>
       <c r="N16" t="n">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9172</v>
+        <v>2.1037</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7713</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3531</v>
+        <v>0.3942</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9172</v>
+        <v>2.1037</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9172</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.1989</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9172</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9261</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.1989</v>
       </c>
       <c r="K17" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9261</v>
+        <v>2.1013</v>
       </c>
       <c r="N17" t="n">
-        <v>211</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8939</v>
+        <v>2.0569</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7619</v>
+        <v>0.8275</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3437</v>
+        <v>0.3756</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8939</v>
+        <v>2.0569</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1321</v>
+        <v>1.9803</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7618</v>
+        <v>0.0766</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1321</v>
+        <v>1.9803</v>
       </c>
       <c r="I18" t="n">
-        <v>1.148</v>
+        <v>1.9803</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7618</v>
+        <v>0.0766</v>
       </c>
       <c r="K18" t="n">
-        <v>231</v>
+        <v>159</v>
       </c>
       <c r="L18" t="n">
-        <v>257</v>
+        <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9098</v>
+        <v>2.0569</v>
       </c>
       <c r="N18" t="n">
-        <v>488</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8866</v>
+        <v>1.91</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7589</v>
+        <v>0.7684</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3408</v>
+        <v>0.317</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8866</v>
+        <v>1.91</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3273</v>
+        <v>1.91</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4407</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3273</v>
+        <v>1.91</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8864</v>
+        <v>1.9261</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4407</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L19" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4457</v>
+        <v>1.9261</v>
       </c>
       <c r="N19" t="n">
-        <v>285</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8555</v>
+        <v>1.8866</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7464</v>
+        <v>0.7589</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3282</v>
+        <v>0.3077</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8555</v>
+        <v>1.8866</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8555</v>
+        <v>2.3273</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.4407</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8555</v>
+        <v>2.3273</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8555</v>
+        <v>1.8864</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.4407</v>
       </c>
       <c r="K20" t="n">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8555</v>
+        <v>1.4457</v>
       </c>
       <c r="N20" t="n">
-        <v>127</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7842</v>
+        <v>1.8813</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7178</v>
+        <v>0.7568</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2994</v>
+        <v>0.3056</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7842</v>
+        <v>1.8813</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3216</v>
+        <v>1.1195</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5374</v>
+        <v>0.7618</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3216</v>
+        <v>1.1195</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3324</v>
+        <v>1.148</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5374</v>
+        <v>0.7618</v>
       </c>
       <c r="K21" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="L21" t="n">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="M21" t="n">
-        <v>1.795</v>
+        <v>1.9098</v>
       </c>
       <c r="N21" t="n">
-        <v>231</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6605</v>
+        <v>1.8702</v>
       </c>
       <c r="C22" t="n">
-        <v>0.668</v>
+        <v>0.7523</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2494</v>
+        <v>0.3012</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6605</v>
+        <v>1.8702</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5839</v>
+        <v>1.8702</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0766</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5839</v>
+        <v>1.8702</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5839</v>
+        <v>1.8702</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0766</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="L22" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6605</v>
+        <v>1.8702</v>
       </c>
       <c r="N22" t="n">
-        <v>211</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.6472</v>
+        <v>1.8555</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6626</v>
+        <v>0.7464</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2441</v>
+        <v>0.2953</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6472</v>
+        <v>1.8555</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6472</v>
+        <v>1.8555</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6472</v>
+        <v>1.8555</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6472</v>
+        <v>1.8555</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6472</v>
+        <v>1.8555</v>
       </c>
       <c r="N23" t="n">
         <v>127</v>
@@ -1504,369 +1504,369 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6137</v>
+        <v>1.7852</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6492</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2305</v>
+        <v>0.2673</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6137</v>
+        <v>1.7852</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6137</v>
+        <v>1.7852</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6137</v>
+        <v>1.7852</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6212</v>
+        <v>1.7852</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6212</v>
+        <v>1.7852</v>
       </c>
       <c r="N24" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5938</v>
+        <v>1.7755</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6412</v>
+        <v>0.7143</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2225</v>
+        <v>0.2634</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5938</v>
+        <v>1.7755</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5938</v>
+        <v>2.3129</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.5374</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5938</v>
+        <v>2.3129</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5938</v>
+        <v>2.3324</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.5374</v>
       </c>
       <c r="K25" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M25" t="n">
-        <v>1.5938</v>
+        <v>1.795</v>
       </c>
       <c r="N25" t="n">
-        <v>155</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4511</v>
+        <v>1.6472</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5838</v>
+        <v>0.6626</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1648</v>
+        <v>0.2123</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4511</v>
+        <v>1.6472</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4511</v>
+        <v>1.6472</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4511</v>
+        <v>1.6472</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4511</v>
+        <v>1.6472</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>187</v>
+        <v>127</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4511</v>
+        <v>1.6472</v>
       </c>
       <c r="N26" t="n">
-        <v>187</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3594</v>
+        <v>1.6077</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6468</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1278</v>
+        <v>0.1966</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3594</v>
+        <v>1.6077</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3594</v>
+        <v>1.6077</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3594</v>
+        <v>1.6077</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3594</v>
+        <v>1.6212</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3594</v>
+        <v>1.6212</v>
       </c>
       <c r="N27" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3191</v>
+        <v>1.3594</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1115</v>
+        <v>0.0977</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3191</v>
+        <v>1.3594</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3191</v>
+        <v>1.3594</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3191</v>
+        <v>1.3594</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3191</v>
+        <v>1.3594</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3191</v>
+        <v>1.3594</v>
       </c>
       <c r="N28" t="n">
-        <v>157</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.217</v>
+        <v>1.3191</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4896</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0703</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.217</v>
+        <v>1.3191</v>
       </c>
       <c r="F29" t="n">
-        <v>1.371</v>
+        <v>1.3191</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.154</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.371</v>
+        <v>1.3191</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1112</v>
+        <v>1.3191</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.154</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9571999999999999</v>
+        <v>1.3191</v>
       </c>
       <c r="N29" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1734</v>
+        <v>1.217</v>
       </c>
       <c r="C30" t="n">
-        <v>0.472</v>
+        <v>0.4896</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0527</v>
+        <v>0.0409</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1734</v>
+        <v>1.217</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1734</v>
+        <v>1.371</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.154</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1734</v>
+        <v>1.371</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1734</v>
+        <v>1.1112</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.154</v>
       </c>
       <c r="K30" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1734</v>
+        <v>0.9571999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1185</v>
+        <v>1.1734</v>
       </c>
       <c r="C31" t="n">
-        <v>0.45</v>
+        <v>0.472</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0305</v>
+        <v>0.0236</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1185</v>
+        <v>1.1734</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1185</v>
+        <v>1.1734</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1185</v>
+        <v>1.1734</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1185</v>
+        <v>1.1734</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1185</v>
+        <v>1.1734</v>
       </c>
       <c r="N31" t="n">
-        <v>189</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9977</v>
+        <v>1.0629</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4014</v>
+        <v>0.4276</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0183</v>
+        <v>-0.0205</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9977</v>
+        <v>1.0629</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9977</v>
+        <v>1.0629</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9977</v>
+        <v>1.0629</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9977</v>
+        <v>1.0629</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9977</v>
+        <v>1.0629</v>
       </c>
       <c r="N32" t="n">
         <v>77</v>
@@ -1918,553 +1918,553 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9062</v>
+        <v>0.9377</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3645</v>
+        <v>0.3772</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0553</v>
+        <v>-0.0703</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9062</v>
+        <v>0.9377</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9062</v>
+        <v>0.9377</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9062</v>
+        <v>0.9377</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9062</v>
+        <v>0.9377</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9062</v>
+        <v>0.9377</v>
       </c>
       <c r="N33" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8129</v>
+        <v>0.9062</v>
       </c>
       <c r="C34" t="n">
-        <v>0.327</v>
+        <v>0.3645</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.093</v>
+        <v>-0.0829</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8129</v>
+        <v>0.9062</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1126</v>
+        <v>0.9062</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2997</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1126</v>
+        <v>0.9062</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9018</v>
+        <v>0.9062</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2997</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="L34" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6021000000000001</v>
+        <v>0.9062</v>
       </c>
       <c r="N34" t="n">
-        <v>285</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.792</v>
+        <v>0.8629</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3186</v>
+        <v>0.3471</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1014</v>
+        <v>-0.1001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.792</v>
+        <v>0.8629</v>
       </c>
       <c r="F35" t="n">
-        <v>0.792</v>
+        <v>1.1626</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.2997</v>
       </c>
       <c r="H35" t="n">
-        <v>0.792</v>
+        <v>1.1626</v>
       </c>
       <c r="I35" t="n">
-        <v>0.792</v>
+        <v>0.9423</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.2997</v>
       </c>
       <c r="K35" t="n">
+        <v>208</v>
+      </c>
+      <c r="L35" t="n">
         <v>77</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
-        <v>0.792</v>
+        <v>0.6426000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>77</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7663</v>
+        <v>0.8444</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3083</v>
+        <v>0.3397</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1118</v>
+        <v>-0.1075</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7663</v>
+        <v>0.8444</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7663</v>
+        <v>1.4161</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7663</v>
+        <v>1.4161</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7663</v>
+        <v>1.428</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="K36" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7663</v>
+        <v>0.8563</v>
       </c>
       <c r="N36" t="n">
-        <v>189</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7159</v>
+        <v>0.792</v>
       </c>
       <c r="C37" t="n">
-        <v>0.288</v>
+        <v>0.3186</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1322</v>
+        <v>-0.1284</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7159</v>
+        <v>0.792</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7159</v>
+        <v>0.792</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7159</v>
+        <v>0.792</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7192</v>
+        <v>0.792</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7192</v>
+        <v>0.792</v>
       </c>
       <c r="N37" t="n">
-        <v>211</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6907</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2779</v>
+        <v>0.2869</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1423</v>
+        <v>-0.1598</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6907</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6907</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6907</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6907</v>
+        <v>0.7192</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6907</v>
+        <v>0.7192</v>
       </c>
       <c r="N38" t="n">
-        <v>189</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6879</v>
+        <v>0.6907</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2767</v>
+        <v>0.2779</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1435</v>
+        <v>-0.1687</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6879</v>
+        <v>0.6907</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6879</v>
+        <v>0.6907</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6879</v>
+        <v>0.6907</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6879</v>
+        <v>0.6907</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6879</v>
+        <v>0.6907</v>
       </c>
       <c r="N39" t="n">
-        <v>69</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5855</v>
+        <v>0.6879</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2355</v>
+        <v>0.2767</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1848</v>
+        <v>-0.1699</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5855</v>
+        <v>0.6879</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5855</v>
+        <v>0.6879</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5855</v>
+        <v>0.6879</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5855</v>
+        <v>0.6879</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5855</v>
+        <v>0.6879</v>
       </c>
       <c r="N40" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5831</v>
+        <v>0.5855</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2346</v>
+        <v>0.2355</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1858</v>
+        <v>-0.2106</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5831</v>
+        <v>0.5855</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5831</v>
+        <v>0.5855</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5831</v>
+        <v>0.5855</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5831</v>
+        <v>0.5855</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5831</v>
+        <v>0.5855</v>
       </c>
       <c r="N41" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DickStacy</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5389</v>
+        <v>0.5831</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2168</v>
+        <v>0.2346</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2037</v>
+        <v>-0.2116</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5389</v>
+        <v>0.5831</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5389</v>
+        <v>0.5831</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5389</v>
+        <v>0.5831</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5389</v>
+        <v>0.5831</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5389</v>
+        <v>0.5831</v>
       </c>
       <c r="N42" t="n">
-        <v>85</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>DickStacy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4652</v>
+        <v>0.5389</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1871</v>
+        <v>0.2168</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2334</v>
+        <v>-0.2292</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4652</v>
+        <v>0.5389</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.0411</v>
+        <v>0.5389</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5063</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.0411</v>
+        <v>0.5389</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0417</v>
+        <v>0.5389</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5063</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="L43" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4646</v>
+        <v>0.5389</v>
       </c>
       <c r="N43" t="n">
-        <v>488</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4589</v>
+        <v>0.4656</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1846</v>
+        <v>0.1873</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.236</v>
+        <v>-0.2584</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4589</v>
+        <v>0.4656</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0306</v>
+        <v>-0.0407</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.5717</v>
+        <v>0.5063</v>
       </c>
       <c r="H44" t="n">
-        <v>1.0306</v>
+        <v>-0.0407</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0354</v>
+        <v>-0.0417</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.5717</v>
+        <v>0.5063</v>
       </c>
       <c r="K44" t="n">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="L44" t="n">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4637000000000001</v>
+        <v>0.4646</v>
       </c>
       <c r="N44" t="n">
-        <v>231</v>
+        <v>488</v>
       </c>
     </row>
     <row r="45">
@@ -2480,7 +2480,7 @@
         <v>0.1619</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2588</v>
+        <v>-0.2836</v>
       </c>
       <c r="E45" t="n">
         <v>0.4025</v>
@@ -2526,7 +2526,7 @@
         <v>0.1308</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.29</v>
+        <v>-0.3144</v>
       </c>
       <c r="E46" t="n">
         <v>0.3252</v>
@@ -2572,7 +2572,7 @@
         <v>0.083</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3381</v>
+        <v>-0.3618</v>
       </c>
       <c r="E47" t="n">
         <v>0.2062</v>
@@ -2618,7 +2618,7 @@
         <v>0.0603</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3608</v>
+        <v>-0.3842</v>
       </c>
       <c r="E48" t="n">
         <v>0.1499</v>
@@ -2664,7 +2664,7 @@
         <v>0.0494</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3717</v>
+        <v>-0.3949</v>
       </c>
       <c r="E49" t="n">
         <v>0.1229</v>
@@ -2710,7 +2710,7 @@
         <v>0.0228</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3985</v>
+        <v>-0.4213</v>
       </c>
       <c r="E50" t="n">
         <v>0.0567</v>
@@ -2746,446 +2746,446 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0372</v>
+        <v>0.0375</v>
       </c>
       <c r="C51" t="n">
-        <v>0.015</v>
+        <v>0.0151</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4063</v>
+        <v>-0.429</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0372</v>
+        <v>0.0375</v>
       </c>
       <c r="F51" t="n">
-        <v>1.0372</v>
+        <v>0.0375</v>
       </c>
       <c r="G51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.0372</v>
+        <v>0.0375</v>
       </c>
       <c r="I51" t="n">
-        <v>1.042</v>
+        <v>0.0375</v>
       </c>
       <c r="J51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="L51" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.04200000000000004</v>
+        <v>0.0375</v>
       </c>
       <c r="N51" t="n">
-        <v>231</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0144</v>
+        <v>0.0333</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0058</v>
+        <v>0.0134</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4272</v>
+        <v>-0.4306</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0144</v>
+        <v>0.0333</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0144</v>
+        <v>1.0333</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0144</v>
+        <v>1.0333</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0144</v>
+        <v>1.042</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K52" t="n">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0144</v>
+        <v>0.04200000000000004</v>
       </c>
       <c r="N52" t="n">
-        <v>73</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0208</v>
+        <v>-0.0144</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4298</v>
+        <v>-0.4496</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0208</v>
+        <v>-0.0144</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0208</v>
+        <v>-0.0144</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0208</v>
+        <v>-0.0144</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0208</v>
+        <v>-0.0144</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0208</v>
+        <v>-0.0144</v>
       </c>
       <c r="N53" t="n">
-        <v>157</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1241</v>
+        <v>-0.0175</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0499</v>
+        <v>-0.007</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4715</v>
+        <v>-0.4509</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1241</v>
+        <v>-0.0175</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1241</v>
+        <v>0.8095</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.827</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1241</v>
+        <v>0.8095</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1241</v>
+        <v>0.8095</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.827</v>
       </c>
       <c r="K54" t="n">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1241</v>
+        <v>-0.01749999999999996</v>
       </c>
       <c r="N54" t="n">
-        <v>85</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2064</v>
+        <v>-0.0208</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.083</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5047</v>
+        <v>-0.4522</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2064</v>
+        <v>-0.0208</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2064</v>
+        <v>-0.0208</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2064</v>
+        <v>-0.0208</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2064</v>
+        <v>-0.0208</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2064</v>
+        <v>-0.0208</v>
       </c>
       <c r="N55" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2137</v>
+        <v>-0.1241</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.0499</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5077</v>
+        <v>-0.4934</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2137</v>
+        <v>-0.1241</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6133</v>
+        <v>-0.1241</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.827</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6133</v>
+        <v>-0.1241</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6133</v>
+        <v>-0.1241</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.827</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="L56" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2137</v>
+        <v>-0.1241</v>
       </c>
       <c r="N56" t="n">
-        <v>211</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2463</v>
+        <v>-0.2064</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.083</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5209</v>
+        <v>-0.5261</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2463</v>
+        <v>-0.2064</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2463</v>
+        <v>-0.2064</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2463</v>
+        <v>-0.2064</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2463</v>
+        <v>-0.2064</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2463</v>
+        <v>-0.2064</v>
       </c>
       <c r="N57" t="n">
-        <v>189</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2512</v>
+        <v>-0.2271</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1011</v>
+        <v>-0.0914</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5228</v>
+        <v>-0.5344</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2512</v>
+        <v>-0.2271</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2512</v>
+        <v>-0.2271</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2512</v>
+        <v>-0.2271</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2512</v>
+        <v>-0.2271</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2512</v>
+        <v>-0.2271</v>
       </c>
       <c r="N58" t="n">
-        <v>85</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.2548</v>
+        <v>-0.2512</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1025</v>
+        <v>-0.1011</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5243</v>
+        <v>-0.544</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2548</v>
+        <v>-0.2512</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2548</v>
+        <v>-0.2512</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2548</v>
+        <v>-0.2512</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2548</v>
+        <v>-0.2512</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2548</v>
+        <v>-0.2512</v>
       </c>
       <c r="N59" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3807</v>
+        <v>-0.2548</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1531</v>
+        <v>-0.1025</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5752</v>
+        <v>-0.5454</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3807</v>
+        <v>-0.2548</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3807</v>
+        <v>-0.2548</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3807</v>
+        <v>-0.2548</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3807</v>
+        <v>-0.2548</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3807</v>
+        <v>-0.2548</v>
       </c>
       <c r="N60" t="n">
         <v>73</v>
@@ -3206,369 +3206,369 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nukkye</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5354</v>
+        <v>-0.3807</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2154</v>
+        <v>-0.1531</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6377</v>
+        <v>-0.5956</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5354</v>
+        <v>-0.3807</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5354</v>
+        <v>-0.3807</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5354</v>
+        <v>-0.3807</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5354</v>
+        <v>-0.3807</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5354</v>
+        <v>-0.3807</v>
       </c>
       <c r="N61" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>nukkye</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5414</v>
+        <v>-0.5354</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2178</v>
+        <v>-0.2154</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6401</v>
+        <v>-0.6572</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5414</v>
+        <v>-0.5354</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5414</v>
+        <v>-0.5354</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5414</v>
+        <v>-0.5354</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5414</v>
+        <v>-0.5354</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5414</v>
+        <v>-0.5354</v>
       </c>
       <c r="N62" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tiburci0</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.642</v>
+        <v>-0.5414</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2583</v>
+        <v>-0.2178</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6807</v>
+        <v>-0.6596</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.642</v>
+        <v>-0.5414</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.642</v>
+        <v>-0.5414</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.642</v>
+        <v>-0.5414</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.642</v>
+        <v>-0.5414</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.642</v>
+        <v>-0.5414</v>
       </c>
       <c r="N63" t="n">
-        <v>69</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>tiburci0</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7137</v>
+        <v>-0.642</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2871</v>
+        <v>-0.2583</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7097</v>
+        <v>-0.6997</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7137</v>
+        <v>-0.642</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7137</v>
+        <v>-0.642</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7137</v>
+        <v>-0.642</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7137</v>
+        <v>-0.642</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7137</v>
+        <v>-0.642</v>
       </c>
       <c r="N64" t="n">
-        <v>187</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7164</v>
+        <v>-0.7137</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2882</v>
+        <v>-0.2871</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7108</v>
+        <v>-0.7282</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7164</v>
+        <v>-0.7137</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2836</v>
+        <v>-0.7137</v>
       </c>
       <c r="G65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2836</v>
+        <v>-0.7137</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2836</v>
+        <v>-0.7137</v>
       </c>
       <c r="J65" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="L65" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7163999999999999</v>
+        <v>-0.7137</v>
       </c>
       <c r="N65" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7653</v>
+        <v>-0.7164</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3079</v>
+        <v>-0.2882</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7305</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7653</v>
+        <v>-0.7164</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7653</v>
+        <v>0.2836</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7653</v>
+        <v>0.2836</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7653</v>
+        <v>0.2836</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K66" t="n">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7653</v>
+        <v>-0.7163999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>77</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8842</v>
+        <v>-0.7653</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3557</v>
+        <v>-0.3079</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7786</v>
+        <v>-0.7488</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8842</v>
+        <v>-0.7653</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8842</v>
+        <v>-0.7653</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8842</v>
+        <v>-0.7653</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8842</v>
+        <v>-0.7653</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8842</v>
+        <v>-0.7653</v>
       </c>
       <c r="N67" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8873</v>
+        <v>-0.8842</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3569</v>
+        <v>-0.3557</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7798</v>
+        <v>-0.7962</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8873</v>
+        <v>-0.8842</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8873</v>
+        <v>-0.8842</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8873</v>
+        <v>-0.8842</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8873</v>
+        <v>-0.8842</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8873</v>
+        <v>-0.8842</v>
       </c>
       <c r="N68" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -3584,7 +3584,7 @@
         <v>-0.374</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.8143</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9296</v>
@@ -3630,7 +3630,7 @@
         <v>-0.4328</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.856</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0758</v>
@@ -3676,7 +3676,7 @@
         <v>-0.433</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8562</v>
+        <v>-0.8727</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0764</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4409</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8641</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="E72" t="n">
         <v>-1.0959</v>
@@ -3768,7 +3768,7 @@
         <v>-0.4456</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8688</v>
+        <v>-0.8852</v>
       </c>
       <c r="E73" t="n">
         <v>-1.1076</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1917</v>
+        <v>-1.1872</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4794</v>
+        <v>-0.4776</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9028</v>
+        <v>-0.9169</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1917</v>
+        <v>-1.1872</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1917</v>
+        <v>-1.1872</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1917</v>
+        <v>-1.1872</v>
       </c>
       <c r="I74" t="n">
         <v>-1.1972</v>
@@ -3860,7 +3860,7 @@
         <v>-0.517</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9405</v>
+        <v>-0.9559</v>
       </c>
       <c r="E75" t="n">
         <v>-1.2851</v>
@@ -3906,7 +3906,7 @@
         <v>-0.5338000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9574</v>
+        <v>-0.9725</v>
       </c>
       <c r="E76" t="n">
         <v>-1.3269</v>
@@ -3952,7 +3952,7 @@
         <v>-0.5605</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9842</v>
+        <v>-0.999</v>
       </c>
       <c r="E77" t="n">
         <v>-1.3933</v>
@@ -3998,7 +3998,7 @@
         <v>-0.6515</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0756</v>
+        <v>-1.0891</v>
       </c>
       <c r="E78" t="n">
         <v>-1.6195</v>
@@ -4044,7 +4044,7 @@
         <v>-0.6912</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1155</v>
+        <v>-1.1284</v>
       </c>
       <c r="E79" t="n">
         <v>-1.7182</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.5243</v>
+        <v>-2.5148</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.0155</v>
+        <v>-1.0117</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4411</v>
+        <v>-1.4458</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.5243</v>
+        <v>-2.5148</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.5243</v>
+        <v>-2.5148</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.5243</v>
+        <v>-2.5148</v>
       </c>
       <c r="I80" t="n">
         <v>-2.536</v>
@@ -4136,7 +4136,7 @@
         <v>-1.4024</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8297</v>
+        <v>-1.8328</v>
       </c>
       <c r="E81" t="n">
         <v>-3.4861</v>
